--- a/автономные контроллеры/101/лог ремонта.xlsx
+++ b/автономные контроллеры/101/лог ремонта.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>R 11</t>
   </si>
@@ -85,6 +85,33 @@
   </si>
   <si>
     <t>не запуск, маленькая амплитуда на кварце  13 нога</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>VD10</t>
+  </si>
+  <si>
+    <t>НЕТ ЗЕМЛИ!!!</t>
+  </si>
+  <si>
+    <t>DA1</t>
+  </si>
+  <si>
+    <t>шумы, низкая дальность, высокое напряжение, почти питание, на 1 ноге</t>
+  </si>
+  <si>
+    <t>низкое потребление, 0В на D1</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>низкое потребление, нет частоты на процессоре</t>
+  </si>
+  <si>
+    <t>dd1</t>
   </si>
 </sst>
 </file>
@@ -121,8 +148,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -130,7 +163,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,9 +462,9 @@
   <dimension ref="B1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="15.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" style="1" customWidth="1"/>
@@ -440,31 +473,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="5"/>
+      <c r="I1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="2"/>
+      <c r="J1" s="5"/>
     </row>
     <row r="2" spans="2:10">
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -490,64 +523,94 @@
       <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="60">
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" ht="30">
+      <c r="F5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="90">
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="2:10">
+      <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="60">
       <c r="B7" t="s">
         <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="2:10">
